--- a/manuscript_material/source_data/Source_Data_ED_Fig3.xlsx
+++ b/manuscript_material/source_data/Source_Data_ED_Fig3.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="a_failure_phase" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="a_after_no_message" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="b_failed_calls_by_cause" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="c_tools_with_changed_values" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="c_parameter_substitution_by_too" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="d_engineering_targets" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
@@ -505,7 +505,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>failed_jobs</t>
+          <t>galaxy_job_errors</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Tool description needs a history</t>
+          <t>Tool description needs an analysis history</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -759,7 +759,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dataset or history identifier</t>
+          <t>Dataset or analysis-history identifier</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -993,7 +993,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Tool description needs a history</t>
+          <t>Tool description needs an analysis history</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1097,7 +1097,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Dataset or history identifier</t>
+          <t>Dataset or analysis-history identifier</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1331,7 +1331,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Tool description needs a history</t>
+          <t>Tool description needs an analysis history</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1435,7 +1435,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Dataset or history identifier</t>
+          <t>Dataset or analysis-history identifier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>ran_with_changed_values</t>
+          <t>executed_with_substitution</t>
         </is>
       </c>
     </row>
@@ -1993,12 +1993,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4,352 differences; 916 jobs ran with them</t>
+          <t>4,352 parameter substitutions; 916 executed</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jobs run with unreported differences = 0</t>
+          <t>Executed parameter substitutions = 0</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Serve tool descriptions without requiring a history</t>
+          <t>Serve tool descriptions without requiring an analysis history</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2039,7 +2039,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Return an error message for every failed job</t>
+          <t>Return an error message for every Galaxy job error</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>bix-45-q1 (0 of 15 accepted); bix-28-q3 (a variance read as a median)</t>
+          <t>bix-45-q1 (0 of 15 scored correct); bix-28-q3 (a variance read as a median)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">

--- a/manuscript_material/source_data/Source_Data_ED_Fig3.xlsx
+++ b/manuscript_material/source_data/Source_Data_ED_Fig3.xlsx
@@ -2078,7 +2078,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>bix-45-q1 (0 of 15 scored correct); bix-28-q3 (a variance read as a median)</t>
+          <t>bix-45-q1: 0 of 15 scored correct; bix-28-q3: a variance read as a median</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
